--- a/Donnees/Pauvreté et condition de vie/Pauvreté/Theme_Pauvreté.xlsx
+++ b/Donnees/Pauvreté et condition de vie/Pauvreté/Theme_Pauvreté.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Pauvreté et condition de vie\Pauvreté\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CA18D3-4AE0-4C12-A74C-AA9141700159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D9F8B3-B918-47A1-BB64-951229E36634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,22 +76,10 @@
     <t>Tableau 2.1.7: Indice de Gini par wilaya et milieu de résidence 2000-2019</t>
   </si>
   <si>
-    <t>Tableau 2.1.8: Incidence de la pauvreté (H) (en 2019) par wilaya et milieu de résidence</t>
-  </si>
-  <si>
     <t>Valeur</t>
   </si>
   <si>
-    <t>Intervalle de Confiance (95%)</t>
-  </si>
-  <si>
     <t>Source : EPCV/2019</t>
-  </si>
-  <si>
-    <t>Tableau 2.1.9: Intensité de la pauvreté (A) (en 2019) par wilaya et milieu de résidence</t>
-  </si>
-  <si>
-    <t>Tableau 2.1.10: Indice de pauvreté multidimensionnelle (IPM-M) (en 2019) par wilaya et milieu de résidence</t>
   </si>
   <si>
     <t>Total</t>
@@ -134,6 +122,18 @@
   </si>
   <si>
     <t>Wilaya~Nouakchott</t>
+  </si>
+  <si>
+    <t>Intervalle de confiance (95%)</t>
+  </si>
+  <si>
+    <t>Tableau 2.1.8: Incidence de la pauvreté (H) par wilaya et milieu de résidence 2019</t>
+  </si>
+  <si>
+    <t>Tableau 2.1.9: Intensité de la pauvreté (A) par wilaya et milieu de résidence 2019</t>
+  </si>
+  <si>
+    <t>Tableau 2.1.10: Indice de pauvreté multidimensionnelle (IPM-M) par wilaya et milieu de résidence 2019</t>
   </si>
 </sst>
 </file>
@@ -519,7 +519,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>51</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>32.9</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>62.6</v>
@@ -619,7 +619,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>70.5</v>
@@ -639,7 +639,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>80</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>62.5</v>
@@ -679,7 +679,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>57.6</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>26.7</v>
@@ -719,7 +719,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>5.6</v>
@@ -739,7 +739,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>52.1</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>83.1</v>
@@ -779,7 +779,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>17.2</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>32.9</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>29.2</v>
@@ -854,21 +854,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>0.32038840000000002</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>0.45112780000000002</v>
@@ -912,7 +912,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0.43616100000000002</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>0.38666889999999998</v>
@@ -934,7 +934,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>0.46001829999999999</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>0.34024359999999998</v>
@@ -956,7 +956,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0.20221710000000001</v>
@@ -967,7 +967,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.22870689999999999</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.12572369999999999</v>
@@ -989,7 +989,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0.37284460000000003</v>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>0.57655000000000001</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>0.1221117</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>0.1363819</v>
@@ -1033,7 +1033,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>0.14937349999999999</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>19.3</v>
@@ -1142,7 +1142,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>10.5</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>25.1</v>
@@ -1182,7 +1182,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>30.4</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>35.9</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>22.9</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>20.8</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>15.1</v>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>38</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>4.4000000000000004</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>8.9</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>7.6</v>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>9.6</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>4.7</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>13</v>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>16.100000000000001</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>19.399999999999999</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>11</v>
@@ -1600,7 +1600,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>9.9</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>1.9</v>
@@ -1640,7 +1640,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.3</v>
@@ -1660,7 +1660,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>6.2</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>17.100000000000001</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>1.7</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>3.2</v>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>2.9</v>
@@ -1798,7 +1798,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>34.1</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>19.100000000000001</v>
@@ -1878,7 +1878,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>44.5</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>53.4</v>
@@ -1918,7 +1918,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>62.4</v>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>42.8</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>37.5</v>
@@ -1978,7 +1978,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>10.3</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>1.2</v>
@@ -2018,7 +2018,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>28.6</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>62.5</v>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>6.9</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>18.899999999999999</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>13.8</v>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>11.1</v>
@@ -2216,7 +2216,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>5.0999999999999996</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>15.2</v>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>18.899999999999999</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>22.8</v>
@@ -2296,7 +2296,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>12.8</v>
@@ -2316,7 +2316,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>11.6</v>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>1.6</v>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.3</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>6.5</v>
@@ -2396,7 +2396,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>25.4</v>
@@ -2416,7 +2416,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>1.9</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>3.2</v>
@@ -2456,7 +2456,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>2.9</v>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>4.9000000000000004</v>
@@ -2574,7 +2574,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>2.1</v>
@@ -2594,7 +2594,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>8.8000000000000007</v>
@@ -2634,7 +2634,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>10.9</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>5.2</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>4.5999999999999996</v>
@@ -2694,7 +2694,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.4</v>
@@ -2714,7 +2714,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.1</v>
@@ -2734,7 +2734,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>2.4</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>13.1</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>0.6</v>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>0.8</v>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>0.9</v>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>0.39</v>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>0.35699999999999998</v>
@@ -2952,7 +2952,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0.36799999999999999</v>
@@ -2972,7 +2972,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>0.38100000000000001</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>0.32300000000000001</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>0.33</v>
@@ -3032,7 +3032,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0.33700000000000002</v>
@@ -3052,7 +3052,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.27300000000000002</v>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.30399999999999999</v>
@@ -3092,7 +3092,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0.34</v>
@@ -3112,7 +3112,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>0.33700000000000002</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>0.372</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>0.34899999999999998</v>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>0.34599999999999997</v>
@@ -3207,21 +3207,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>0.56915769999999999</v>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>0.77812899999999996</v>
@@ -3265,7 +3265,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0.74322429999999995</v>
@@ -3276,7 +3276,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>0.67289150000000009</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>0.79675619999999991</v>
@@ -3298,7 +3298,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>0.62085920000000006</v>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0.39948040000000001</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.44408199999999998</v>
@@ -3331,7 +3331,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.26445170000000001</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0.6444217000000001</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>0.90215380000000001</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>0.25155159999999999</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>0.28498410000000002</v>
@@ -3386,7 +3386,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>0.30702449999999998</v>
@@ -3397,7 +3397,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3412,21 +3412,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>0.56291679999999999</v>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>0.57975960000000004</v>
@@ -3470,7 +3470,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0.58684970000000003</v>
@@ -3481,7 +3481,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>0.57463779999999998</v>
@@ -3492,7 +3492,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>0.57736399999999999</v>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>0.54802050000000002</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0.50620039999999999</v>
@@ -3525,7 +3525,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.51501059999999999</v>
@@ -3536,7 +3536,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.47541260000000002</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0.57857250000000005</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>0.63908169999999997</v>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>0.48543409999999998</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>0.47855979999999998</v>
@@ -3591,7 +3591,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>0.4865197</v>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
